--- a/artfynd/A 48167-2022 artfynd.xlsx
+++ b/artfynd/A 48167-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123671738</v>
+        <v>123671798</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -726,7 +726,7 @@
         <v>621699</v>
       </c>
       <c r="R2" t="n">
-        <v>6659921</v>
+        <v>6659886</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123671798</v>
+        <v>123671738</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,7 +823,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,7 +836,7 @@
         <v>621699</v>
       </c>
       <c r="R3" t="n">
-        <v>6659886</v>
+        <v>6659921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,6 +869,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 48167-2022 artfynd.xlsx
+++ b/artfynd/A 48167-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123671798</v>
+        <v>123671738</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -726,7 +726,7 @@
         <v>621699</v>
       </c>
       <c r="R2" t="n">
-        <v>6659886</v>
+        <v>6659921</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123671738</v>
+        <v>123671798</v>
       </c>
       <c r="B3" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,7 +828,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -836,7 +841,7 @@
         <v>621699</v>
       </c>
       <c r="R3" t="n">
-        <v>6659921</v>
+        <v>6659886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,11 +874,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 48167-2022 artfynd.xlsx
+++ b/artfynd/A 48167-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123671738</v>
+        <v>123671798</v>
       </c>
       <c r="B2" t="n">
         <v>56700</v>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -726,7 +726,7 @@
         <v>621699</v>
       </c>
       <c r="R2" t="n">
-        <v>6659921</v>
+        <v>6659886</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123671798</v>
+        <v>123671738</v>
       </c>
       <c r="B3" t="n">
         <v>56700</v>
@@ -828,7 +823,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,7 +836,7 @@
         <v>621699</v>
       </c>
       <c r="R3" t="n">
-        <v>6659886</v>
+        <v>6659921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,6 +869,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 48167-2022 artfynd.xlsx
+++ b/artfynd/A 48167-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123671798</v>
+        <v>123671738</v>
       </c>
       <c r="B2" t="n">
         <v>56700</v>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -726,7 +726,7 @@
         <v>621699</v>
       </c>
       <c r="R2" t="n">
-        <v>6659886</v>
+        <v>6659921</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123671738</v>
+        <v>123671798</v>
       </c>
       <c r="B3" t="n">
         <v>56700</v>
@@ -823,7 +828,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -836,7 +841,7 @@
         <v>621699</v>
       </c>
       <c r="R3" t="n">
-        <v>6659921</v>
+        <v>6659886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,11 +874,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Riklig mängd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
